--- a/docs/decisions/Decision Log.xlsx
+++ b/docs/decisions/Decision Log.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4c906530d9ff38bc/Desktop/SEN381/Ticketing-System/docs/decisions/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="43" documentId="8_{DA8A1402-F87E-4E16-A5E2-7754A6675A1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7EC579CB-96B6-4C59-A100-9C8F355961CC}"/>
+  <xr:revisionPtr revIDLastSave="75" documentId="8_{DA8A1402-F87E-4E16-A5E2-7754A6675A1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF98EB54-458B-4C14-B260-760704656EAE}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="17496" xr2:uid="{C10860F7-7028-4DF0-9A0A-0CD539FC6C60}"/>
+    <workbookView xWindow="4548" yWindow="4704" windowWidth="23040" windowHeight="12576" xr2:uid="{C10860F7-7028-4DF0-9A0A-0CD539FC6C60}"/>
   </bookViews>
   <sheets>
     <sheet name="Decision Log" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="72">
   <si>
     <t>Decision Log</t>
   </si>
@@ -225,6 +225,36 @@
   </si>
   <si>
     <t>Ethan</t>
+  </si>
+  <si>
+    <t>2026/09/06  - Revised 2206/09/09</t>
+  </si>
+  <si>
+    <t>Exclude a native mobile application from the committed scope; mobile access is delivered through responsive web</t>
+  </si>
+  <si>
+    <t>Originally taken as a team judgement: a responsive web interface meets the access need within CON-002 and CON-004, and a second build and release path is not supportable by three part-time students within the delivery period. Revised 09/09/2026 — the client confirmed verbally that the solution is to be a web application with mobile access via responsive web (CON-011). The decision is unchanged; its basis is now a client directive rather than a team judgement.</t>
+  </si>
+  <si>
+    <t>Places a usability obligation on the web interface at mobile viewports, to be specified measurably by Member B under CON-005. Following the revision, the exclusion is no longer a team preference and cannot be revisited without a change request under Master Brief s.14. Reduces the risk that scope pressure later reopens the question.</t>
+  </si>
+  <si>
+    <t>DEC-007 (Revised)</t>
+  </si>
+  <si>
+    <t>DEC-009</t>
+  </si>
+  <si>
+    <t>Adopt a controlled process for capturing verbally-issued client requirements: instructions given in session are recorded in dated team notes by a nominated member, committed to the repository within one working day, and confirmed with the client at the next session before being treated as binding.</t>
+  </si>
+  <si>
+    <t>Rely on individual members' personal notes; request that all client instructions be issued in writing; treat verbal instructions as non-binding until they appear in a written brief.</t>
+  </si>
+  <si>
+    <t>The client (STK-010) issues requirements verbally in sessions with no written record on their side. Without a controlled capture process, a directive exists only in individual memory, cannot be traced to a source, and cannot be shown to have been the basis of a requirement or constraint. Requesting written instruction was rejected as outside the team's control. Treating verbal instruction as non-binding was rejected because the instructions are directive in practice and ignoring them would put delivery at risk. Confirming at the next session gives the client an opportunity to correct a misheard or misrecorded instruction before it propagates into requirements.</t>
+  </si>
+  <si>
+    <t>Creates a recurring obligation for the duration of the project, not a one-off task. Introduces up to a one-session lag between an instruction being given and it being treated as binding, which is a deliberate accuracy-over-speed trade-off. Every constraint or requirement derived from a verbal instruction must cite the dated note as its source, so the notes become a controlled artefact subject to the same repository controls as any other. Reduces the risk of disputed or forgotten requirements at later milestones.</t>
   </si>
 </sst>
 </file>
@@ -354,7 +384,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
@@ -397,9 +427,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -429,7 +456,12 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <color rgb="FFA6A6A6"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF7A3E00"/>
@@ -796,15 +828,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51C17EC7-5E25-4DAF-A0FC-95E5CA365EC5}">
-  <dimension ref="B1:N12"/>
+  <dimension ref="B1:N14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.21875" customWidth="1"/>
-    <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="3" max="3" width="19" customWidth="1"/>
+    <col min="2" max="2" width="18.109375" customWidth="1"/>
+    <col min="3" max="3" width="30.21875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="37" customWidth="1"/>
     <col min="5" max="5" width="38.88671875" customWidth="1"/>
-    <col min="6" max="6" width="59.21875" customWidth="1"/>
+    <col min="6" max="6" width="64.88671875" customWidth="1"/>
     <col min="7" max="7" width="53.6640625" customWidth="1"/>
     <col min="8" max="8" width="44.44140625" customWidth="1"/>
     <col min="9" max="9" width="11.109375" customWidth="1"/>
@@ -814,30 +846,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
     </row>
     <row r="2" spans="2:14" x14ac:dyDescent="0.3">
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="21"/>
-      <c r="J2" s="21"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
     </row>
     <row r="4" spans="2:14" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
@@ -867,11 +899,11 @@
       <c r="J4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L4" s="19" t="s">
+      <c r="L4" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="M4" s="19"/>
-      <c r="N4" s="19"/>
+      <c r="M4" s="18"/>
+      <c r="N4" s="18"/>
     </row>
     <row r="5" spans="2:14" ht="90" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
@@ -902,13 +934,13 @@
       <c r="J5" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="L5" s="23" t="s">
+      <c r="L5" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="M5" s="23"/>
+      <c r="M5" s="22"/>
       <c r="N5" s="13">
         <f>COUNTIF($J$5:$J$151,"DECIDED")</f>
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="2:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -940,10 +972,10 @@
       <c r="J6" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="L6" s="23" t="s">
+      <c r="L6" s="22" t="s">
         <v>54</v>
       </c>
-      <c r="M6" s="23"/>
+      <c r="M6" s="22"/>
       <c r="N6" s="13">
         <f>COUNTIF($J$5:$J$12,"DEFERRED")</f>
         <v>3</v>
@@ -978,13 +1010,13 @@
       <c r="J7" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="L7" s="18" t="s">
+      <c r="L7" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="M7" s="18"/>
+      <c r="M7" s="17"/>
       <c r="N7" s="14">
         <f>COUNTA($B$5:$B$149)</f>
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="2:14" ht="57.6" x14ac:dyDescent="0.3">
@@ -1108,32 +1140,91 @@
       </c>
     </row>
     <row r="12" spans="2:14" ht="72" x14ac:dyDescent="0.3">
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="C12" s="17">
+      <c r="C12" s="9">
         <f>DATE(2026,9,8)</f>
         <v>46273</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="D12" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="E12" s="16" t="s">
+      <c r="E12" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="F12" s="16" t="s">
+      <c r="F12" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="G12" s="16" t="s">
+      <c r="G12" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="H12" s="5" t="s">
+      <c r="H12" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="I12" s="6" t="s">
+      <c r="I12" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="J12" s="7" t="s">
+      <c r="J12" s="12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="F13" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="G13" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="J13" s="7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="2:14" ht="160.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14" s="9">
+        <f>DATE(2026,9,9)</f>
+        <v>46274</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="G14" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="H14" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="I14" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="J14" s="12" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1147,22 +1238,27 @@
     <mergeCell ref="L6:M6"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
-  <conditionalFormatting sqref="C5:C11">
+  <conditionalFormatting sqref="C5:C12">
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
+      <formula>"—"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H5:H14">
     <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
       <formula>"—"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H5:H12">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
-      <formula>"—"</formula>
+  <conditionalFormatting sqref="J5:J14">
+    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="DECIDED">
+      <formula>NOT(ISERROR(SEARCH("DECIDED",J5)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="DEFERRED">
+      <formula>NOT(ISERROR(SEARCH("DEFERRED",J5)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J5:J12">
-    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="DECIDED">
-      <formula>NOT(ISERROR(SEARCH("DECIDED",J5)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="DEFERRED">
-      <formula>NOT(ISERROR(SEARCH("DEFERRED",J5)))</formula>
+  <conditionalFormatting sqref="C14">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+      <formula>"—"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
